--- a/sonuclar/arsgor_2026-10-24.xlsx
+++ b/sonuclar/arsgor_2026-10-24.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2B3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +58,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,15 +428,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,7 +471,141 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>YENİ</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ilan.gov.tr</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Kahramanmaraş Sütçü İmam Üniversitesi Araştırma Görevlisi Alım İlanı</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>06.11.2026</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Birimi	Ünvanı	K/D	Adet	ALES PUAN TÜRÜ	Y. Dil	Niteliği | MÜHENDİSLİK – MİMARLIK FAKÜLTESİ | Bilgisayar Mühendisliği Bölümü Bilgisayar Mühendisliği Kurumsal</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilan.gov.tr/ilan/2266584/kamu-akademik-personel-akademik-personel-alimlari-kahramanmaras-sutcu-imam-universitesi-arastirma-gorevlisi-alim-ilani</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>YENİ</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ilan.gov.tr</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Beykent Üniversitesi Rektörlüğünden Araştırma Görevlisi Alım İlanı</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fakültesi	Psikoloji	1	Araştırma Görevlisi	Psikoloji alanında lisans mezunu olup, Psikoloji bölümünün herhangi bir alanında tezli yüksek lisans yapıyor olmak.	ALES:80 YDS:80	EA | Mühendislik-Mimarlık | Fakültesi	Endüstri Mühendisliği (İngilizce)	1	Araştırma Görevlisi	Endüstri Mühendisliği alanında lisans mezunu olup Endüstri Mühendisliği alanında en az tezli yüksek lisans yapıyor olmak.	ALES: 70 | Fen-Edebiyat Fakültesi	444 1997 / 6203	gulsener@beykent.edu.tr | Mühendislik-Mimarlık Fakültesi	444 1997 / 2031	esrademircioglu@beykent.edu.tr | İlan Bilgileri</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilan.gov.tr/ilan/2265131/kamu-akademik-personel-akademik-personel-alimlari-istanbul%C2%A0beykent%C2%A0universitesi%C2%A0rektorlugunden-arastirma-gorevlisi-alim-ilani</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>YENİ</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ilan.gov.tr</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Ege Üniversitesi Rektörlüğünden Öğretim Elemanı Alım İlanı</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06.11.2026</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>tipdekanozelkalem@mail.ege.edu.tr	Deri ve Zührevi Hastalıkları uzmanı olmak. Dermatoloji, Dermoskopi ve In Vivo Konfokal Mikroskopi konularında deneyimli olmak. | 13	Güzel Sanatlar, Tasarım ve Mimarlık Fakültesi	Görsel İletişim | Tasarımı Bölümü	Görsel İletişim Tasarımı Anabilim Dalı	1	6	ÖĞR. GÖR. (D.V.)	Sözel	50	https://gstmt.ege.edu.tr/	0232 311 25 00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilan.gov.tr/ilan/2265055/kamu-akademik-personel-akademik-personel-alimlari-ege%C2%A0universitesi%C2%A0rektorlugunden-ogretim-elemani-alim-ilani</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>YENİ</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ilan.gov.tr</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>İzmir Bakırçay Üniversitesi Rektörlüğünden Öğretim Elemanı Alım İlanı</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1	Araştırma Görevlisi	6	1	75 (EA)	60	Hukuk Fakültesi Kamu Hukuku Bölümü Hukuk Tarihi Anabilim Dalı	Hukuk fakültesi mezunu olmak ve kamu hukuku alanında yüksek lisans yapıyor olmak. | 2	Araştırma Görevlisi	6	1	75 (SAY)	60	Mühendislik ve Mimarlık Fakültesi Endüstri Mühendisliği Bölümü Endüstri Mühendisliği Anabilim Dalı	Endüstri Mühendisliği Bölümü lisans mezunu olmak ve Endüstri Mühendisliği progra</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilan.gov.tr/ilan/2261215/kamu-akademik-personel-akademik-personel-alimlari-izmir%C2%A0bakircay%C2%A0universitesi%C2%A0rektorlugunden-ogretim-elemani-alim-ilani</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>